--- a/EXCEL/Data/Figur_7+8_tabel_6/Tabel_6_klassificering.xlsx
+++ b/EXCEL/Data/Figur_7+8_tabel_6/Tabel_6_klassificering.xlsx
@@ -88,7 +88,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 09.19.02</t>
+    <t>Kørsel 15.4.2026 09.26.14</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
